--- a/excel/Пути на старую волочилку.xlsx
+++ b/excel/Пути на старую волочилку.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Downloads\Telegram Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88761BB1-7B8C-45A3-8C26-7137A671C408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,7 +33,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -85,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +92,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -372,24 +369,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O142"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -436,7 +433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>8</v>
       </c>
@@ -484,7 +481,7 @@
         <v>1.1099999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>8</v>
       </c>
@@ -532,7 +529,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>8</v>
       </c>
@@ -580,7 +577,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>8</v>
       </c>
@@ -628,7 +625,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -676,7 +673,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>8</v>
       </c>
@@ -724,7 +721,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -772,7 +769,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -820,7 +817,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -868,7 +865,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -916,7 +913,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -964,7 +961,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>8</v>
       </c>
@@ -1010,7 +1007,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -1058,7 +1055,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>8</v>
       </c>
@@ -1106,7 +1103,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -1154,7 +1151,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>8</v>
       </c>
@@ -1202,7 +1199,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>8</v>
       </c>
@@ -1248,7 +1245,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>8</v>
       </c>
@@ -1294,7 +1291,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>8</v>
       </c>
@@ -1340,7 +1337,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>8</v>
       </c>
@@ -1386,7 +1383,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>8</v>
       </c>
@@ -1432,7 +1429,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>8</v>
       </c>
@@ -1478,7 +1475,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>8</v>
       </c>
@@ -1526,7 +1523,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>8</v>
       </c>
@@ -1572,7 +1569,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>8</v>
       </c>
@@ -1618,7 +1615,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>8</v>
       </c>
@@ -1664,7 +1661,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>8</v>
       </c>
@@ -1710,7 +1707,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>8</v>
       </c>
@@ -1756,7 +1753,7 @@
         <v>1.3599999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>8</v>
       </c>
@@ -1802,7 +1799,7 @@
         <v>1.3699999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>8</v>
       </c>
@@ -1848,7 +1845,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>8</v>
       </c>
@@ -1894,7 +1891,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>8</v>
       </c>
@@ -1940,7 +1937,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>8</v>
       </c>
@@ -1986,7 +1983,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>8</v>
       </c>
@@ -2032,7 +2029,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>8</v>
       </c>
@@ -2076,7 +2073,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>8</v>
       </c>
@@ -2122,7 +2119,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>8</v>
       </c>
@@ -2166,7 +2163,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>8</v>
       </c>
@@ -2212,7 +2209,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>8</v>
       </c>
@@ -2258,7 +2255,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>8</v>
       </c>
@@ -2302,7 +2299,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>8</v>
       </c>
@@ -2346,7 +2343,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>8</v>
       </c>
@@ -2390,7 +2387,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>8</v>
       </c>
@@ -2434,7 +2431,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>8</v>
       </c>
@@ -2478,7 +2475,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>8</v>
       </c>
@@ -2522,7 +2519,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>8</v>
       </c>
@@ -2566,7 +2563,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>8</v>
       </c>
@@ -2610,7 +2607,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>8</v>
       </c>
@@ -2654,7 +2651,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>8</v>
       </c>
@@ -2698,7 +2695,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>8</v>
       </c>
@@ -2742,7 +2739,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>8</v>
       </c>
@@ -2781,12 +2778,12 @@
       <c r="N52" s="3">
         <v>1.7</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>8</v>
       </c>
@@ -2823,12 +2820,12 @@
       <c r="N53" s="3">
         <v>1.7</v>
       </c>
-      <c r="O53" s="3">
+      <c r="O53" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>8</v>
       </c>
@@ -2865,12 +2862,12 @@
       <c r="N54" s="3">
         <v>1.7</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>8</v>
       </c>
@@ -2909,12 +2906,12 @@
       <c r="N55" s="3">
         <v>1.7</v>
       </c>
-      <c r="O55" s="3">
+      <c r="O55" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>8</v>
       </c>
@@ -2951,12 +2948,12 @@
       <c r="N56" s="3">
         <v>1.7</v>
       </c>
-      <c r="O56" s="3">
+      <c r="O56" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>8</v>
       </c>
@@ -2995,12 +2992,12 @@
       <c r="N57" s="3">
         <v>1.7</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="6">
         <f t="shared" si="1"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>8</v>
       </c>
@@ -3039,12 +3036,12 @@
       <c r="N58" s="3">
         <v>1.73</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="6">
         <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>8</v>
       </c>
@@ -3081,12 +3078,12 @@
       <c r="N59" s="3">
         <v>1.73</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="6">
         <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>8</v>
       </c>
@@ -3123,12 +3120,12 @@
       <c r="N60" s="3">
         <v>1.73</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="6">
         <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>8</v>
       </c>
@@ -3165,12 +3162,12 @@
       <c r="N61" s="3">
         <v>1.73</v>
       </c>
-      <c r="O61" s="3">
+      <c r="O61" s="6">
         <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>8</v>
       </c>
@@ -3207,12 +3204,12 @@
       <c r="N62" s="3">
         <v>1.75</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="6">
         <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>8</v>
       </c>
@@ -3251,12 +3248,12 @@
       <c r="N63" s="3">
         <v>1.75</v>
       </c>
-      <c r="O63" s="3">
+      <c r="O63" s="6">
         <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>8</v>
       </c>
@@ -3293,12 +3290,12 @@
       <c r="N64" s="3">
         <v>1.75</v>
       </c>
-      <c r="O64" s="3">
+      <c r="O64" s="6">
         <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>8</v>
       </c>
@@ -3335,12 +3332,12 @@
       <c r="N65" s="3">
         <v>1.8</v>
       </c>
-      <c r="O65" s="3">
+      <c r="O65" s="6">
         <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>8</v>
       </c>
@@ -3377,12 +3374,12 @@
       <c r="N66" s="3">
         <v>1.8</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="6">
         <f t="shared" ref="O66:O97" si="2">N66-0.02</f>
         <v>1.78</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>8</v>
       </c>
@@ -3419,12 +3416,12 @@
       <c r="N67" s="3">
         <v>1.8</v>
       </c>
-      <c r="O67" s="3">
+      <c r="O67" s="6">
         <f t="shared" si="2"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>8</v>
       </c>
@@ -3461,12 +3458,12 @@
       <c r="N68" s="3">
         <v>1.8</v>
       </c>
-      <c r="O68" s="3">
+      <c r="O68" s="6">
         <f t="shared" si="2"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>8</v>
       </c>
@@ -3503,12 +3500,12 @@
       <c r="N69" s="3">
         <v>1.8</v>
       </c>
-      <c r="O69" s="3">
+      <c r="O69" s="6">
         <f t="shared" si="2"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>8</v>
       </c>
@@ -3545,12 +3542,12 @@
       <c r="N70" s="3">
         <v>1.85</v>
       </c>
-      <c r="O70" s="3">
+      <c r="O70" s="6">
         <f t="shared" si="2"/>
         <v>1.83</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>8</v>
       </c>
@@ -3587,12 +3584,12 @@
       <c r="N71" s="3">
         <v>1.9</v>
       </c>
-      <c r="O71" s="3">
+      <c r="O71" s="6">
         <f t="shared" si="2"/>
         <v>1.88</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>8</v>
       </c>
@@ -3629,12 +3626,12 @@
       <c r="N72" s="3">
         <v>1.92</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="6">
         <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>8</v>
       </c>
@@ -3671,12 +3668,12 @@
       <c r="N73" s="3">
         <v>1.92</v>
       </c>
-      <c r="O73" s="3">
+      <c r="O73" s="6">
         <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>8</v>
       </c>
@@ -3713,12 +3710,12 @@
       <c r="N74" s="3">
         <v>1.95</v>
       </c>
-      <c r="O74" s="3">
+      <c r="O74" s="6">
         <f t="shared" si="2"/>
         <v>1.93</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>8</v>
       </c>
@@ -3755,12 +3752,12 @@
       <c r="N75" s="3">
         <v>1.95</v>
       </c>
-      <c r="O75" s="3">
+      <c r="O75" s="6">
         <f t="shared" si="2"/>
         <v>1.93</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>8</v>
       </c>
@@ -3797,12 +3794,12 @@
       <c r="N76" s="3">
         <v>2</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="6">
         <f t="shared" si="2"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>8</v>
       </c>
@@ -3839,12 +3836,12 @@
       <c r="N77" s="3">
         <v>2</v>
       </c>
-      <c r="O77" s="3">
+      <c r="O77" s="6">
         <f t="shared" si="2"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>8</v>
       </c>
@@ -3881,12 +3878,12 @@
       <c r="N78" s="3">
         <v>2</v>
       </c>
-      <c r="O78" s="3">
+      <c r="O78" s="6">
         <f t="shared" si="2"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>8</v>
       </c>
@@ -3923,12 +3920,12 @@
       <c r="N79" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="O79" s="3">
+      <c r="O79" s="6">
         <f t="shared" si="2"/>
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>8</v>
       </c>
@@ -3965,12 +3962,12 @@
       <c r="N80" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O80" s="3">
+      <c r="O80" s="6">
         <f t="shared" si="2"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>8</v>
       </c>
@@ -4007,12 +4004,12 @@
       <c r="N81" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="6">
         <f t="shared" si="2"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>8</v>
       </c>
@@ -4049,12 +4046,12 @@
       <c r="N82" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O82" s="3">
+      <c r="O82" s="6">
         <f t="shared" si="2"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>8</v>
       </c>
@@ -4089,12 +4086,12 @@
       <c r="N83" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="6">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>8</v>
       </c>
@@ -4129,12 +4126,12 @@
       <c r="N84" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O84" s="3">
+      <c r="O84" s="6">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>8</v>
       </c>
@@ -4171,12 +4168,12 @@
       <c r="N85" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O85" s="3">
+      <c r="O85" s="6">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>8</v>
       </c>
@@ -4213,12 +4210,12 @@
       <c r="N86" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O86" s="3">
+      <c r="O86" s="6">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4251,12 +4248,12 @@
       <c r="N87" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O87" s="3">
+      <c r="O87" s="6">
         <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>8</v>
       </c>
@@ -4291,12 +4288,12 @@
       <c r="N88" s="3">
         <v>2.1</v>
       </c>
-      <c r="O88" s="3">
+      <c r="O88" s="6">
         <f t="shared" si="2"/>
         <v>2.08</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>8</v>
       </c>
@@ -4331,12 +4328,12 @@
       <c r="N89" s="3">
         <v>2.15</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="6">
         <f t="shared" si="2"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>8</v>
       </c>
@@ -4371,12 +4368,12 @@
       <c r="N90" s="3">
         <v>2.15</v>
       </c>
-      <c r="O90" s="3">
+      <c r="O90" s="6">
         <f t="shared" si="2"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>8</v>
       </c>
@@ -4411,12 +4408,12 @@
       <c r="N91" s="3">
         <v>2.15</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="6">
         <f t="shared" si="2"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>8</v>
       </c>
@@ -4451,12 +4448,12 @@
       <c r="N92" s="3">
         <v>2.1800000000000002</v>
       </c>
-      <c r="O92" s="3">
+      <c r="O92" s="6">
         <f t="shared" si="2"/>
         <v>2.16</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>8</v>
       </c>
@@ -4491,12 +4488,12 @@
       <c r="N93" s="3">
         <v>2.1800000000000002</v>
       </c>
-      <c r="O93" s="3">
+      <c r="O93" s="6">
         <f t="shared" si="2"/>
         <v>2.16</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>8</v>
       </c>
@@ -4531,12 +4528,12 @@
       <c r="N94" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="6">
         <f t="shared" si="2"/>
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>8</v>
       </c>
@@ -4571,12 +4568,12 @@
       <c r="N95" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O95" s="3">
+      <c r="O95" s="6">
         <f t="shared" si="2"/>
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>8</v>
       </c>
@@ -4611,12 +4608,12 @@
       <c r="N96" s="3">
         <v>2.25</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="6">
         <f t="shared" si="2"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>8</v>
       </c>
@@ -4651,12 +4648,12 @@
       <c r="N97" s="3">
         <v>2.25</v>
       </c>
-      <c r="O97" s="3">
+      <c r="O97" s="6">
         <f t="shared" si="2"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>8</v>
       </c>
@@ -4691,12 +4688,12 @@
       <c r="N98" s="3">
         <v>2.25</v>
       </c>
-      <c r="O98" s="3">
+      <c r="O98" s="6">
         <f t="shared" ref="O98:O129" si="3">N98-0.02</f>
         <v>2.23</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>8</v>
       </c>
@@ -4731,12 +4728,12 @@
       <c r="N99" s="3">
         <v>2.25</v>
       </c>
-      <c r="O99" s="3">
+      <c r="O99" s="6">
         <f t="shared" si="3"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>8</v>
       </c>
@@ -4771,12 +4768,12 @@
       <c r="N100" s="3">
         <v>2.27</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="6">
         <f t="shared" si="3"/>
         <v>2.25</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>8</v>
       </c>
@@ -4811,12 +4808,12 @@
       <c r="N101" s="3">
         <v>2.2799999999999998</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="6">
         <f t="shared" si="3"/>
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>8</v>
       </c>
@@ -4851,12 +4848,12 @@
       <c r="N102" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="6">
         <f t="shared" si="3"/>
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>8</v>
       </c>
@@ -4891,12 +4888,12 @@
       <c r="N103" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O103" s="3">
+      <c r="O103" s="6">
         <f t="shared" si="3"/>
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>8</v>
       </c>
@@ -4931,12 +4928,12 @@
       <c r="N104" s="3">
         <v>2.35</v>
       </c>
-      <c r="O104" s="3">
+      <c r="O104" s="6">
         <f t="shared" si="3"/>
         <v>2.33</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>8</v>
       </c>
@@ -4969,12 +4966,12 @@
       <c r="N105" s="3">
         <v>2.35</v>
       </c>
-      <c r="O105" s="3">
+      <c r="O105" s="6">
         <f t="shared" si="3"/>
         <v>2.33</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>8</v>
       </c>
@@ -5007,12 +5004,12 @@
       <c r="N106" s="3">
         <v>2.4</v>
       </c>
-      <c r="O106" s="3">
+      <c r="O106" s="6">
         <f t="shared" si="3"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>8</v>
       </c>
@@ -5045,12 +5042,12 @@
       <c r="N107" s="3">
         <v>2.4</v>
       </c>
-      <c r="O107" s="3">
+      <c r="O107" s="6">
         <f t="shared" si="3"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>8</v>
       </c>
@@ -5083,12 +5080,12 @@
       <c r="N108" s="3">
         <v>2.4</v>
       </c>
-      <c r="O108" s="3">
+      <c r="O108" s="6">
         <f t="shared" si="3"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>8</v>
       </c>
@@ -5121,12 +5118,12 @@
       <c r="N109" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O109" s="3">
+      <c r="O109" s="6">
         <f t="shared" si="3"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>8</v>
       </c>
@@ -5159,12 +5156,12 @@
       <c r="N110" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O110" s="3">
+      <c r="O110" s="6">
         <f t="shared" si="3"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>8</v>
       </c>
@@ -5197,12 +5194,12 @@
       <c r="N111" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O111" s="3">
+      <c r="O111" s="6">
         <f t="shared" si="3"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>8</v>
       </c>
@@ -5235,12 +5232,12 @@
       <c r="N112" s="3">
         <v>2.5</v>
       </c>
-      <c r="O112" s="3">
+      <c r="O112" s="6">
         <f t="shared" si="3"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>8</v>
       </c>
@@ -5273,12 +5270,12 @@
       <c r="N113" s="3">
         <v>2.5</v>
       </c>
-      <c r="O113" s="3">
+      <c r="O113" s="6">
         <f t="shared" si="3"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>8</v>
       </c>
@@ -5315,12 +5312,12 @@
       <c r="N114" s="3">
         <v>2.5</v>
       </c>
-      <c r="O114" s="3">
+      <c r="O114" s="6">
         <f t="shared" si="3"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>8</v>
       </c>
@@ -5355,12 +5352,12 @@
       <c r="N115" s="3">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O115" s="3">
+      <c r="O115" s="6">
         <f t="shared" si="3"/>
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>8</v>
       </c>
@@ -5395,12 +5392,12 @@
       <c r="N116" s="3">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O116" s="3">
+      <c r="O116" s="6">
         <f t="shared" si="3"/>
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>8</v>
       </c>
@@ -5433,12 +5430,12 @@
       <c r="N117" s="3">
         <v>2.6</v>
       </c>
-      <c r="O117" s="3">
+      <c r="O117" s="6">
         <f t="shared" si="3"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>8</v>
       </c>
@@ -5471,12 +5468,12 @@
       <c r="N118" s="3">
         <v>2.6</v>
       </c>
-      <c r="O118" s="3">
+      <c r="O118" s="6">
         <f t="shared" si="3"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>8</v>
       </c>
@@ -5509,12 +5506,12 @@
       <c r="N119" s="3">
         <v>2.6</v>
       </c>
-      <c r="O119" s="3">
+      <c r="O119" s="6">
         <f t="shared" si="3"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>8</v>
       </c>
@@ -5547,12 +5544,12 @@
       <c r="N120" s="3">
         <v>2.63</v>
       </c>
-      <c r="O120" s="3">
+      <c r="O120" s="6">
         <f t="shared" si="3"/>
         <v>2.61</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>8</v>
       </c>
@@ -5585,12 +5582,12 @@
       <c r="N121" s="3">
         <v>2.65</v>
       </c>
-      <c r="O121" s="3">
+      <c r="O121" s="6">
         <f t="shared" si="3"/>
         <v>2.63</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>8</v>
       </c>
@@ -5623,12 +5620,12 @@
       <c r="N122" s="3">
         <v>2.7</v>
       </c>
-      <c r="O122" s="3">
+      <c r="O122" s="6">
         <f t="shared" si="3"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>8</v>
       </c>
@@ -5659,12 +5656,12 @@
       <c r="N123" s="3">
         <v>2.7</v>
       </c>
-      <c r="O123" s="3">
+      <c r="O123" s="6">
         <f t="shared" si="3"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>8</v>
       </c>
@@ -5697,12 +5694,12 @@
       <c r="N124" s="3">
         <v>2.7</v>
       </c>
-      <c r="O124" s="3">
+      <c r="O124" s="6">
         <f t="shared" si="3"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>8</v>
       </c>
@@ -5733,12 +5730,12 @@
       <c r="N125" s="3">
         <v>2.7</v>
       </c>
-      <c r="O125" s="3">
+      <c r="O125" s="6">
         <f t="shared" si="3"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>8</v>
       </c>
@@ -5771,12 +5768,12 @@
       <c r="N126" s="3">
         <v>2.7</v>
       </c>
-      <c r="O126" s="3">
+      <c r="O126" s="6">
         <f t="shared" si="3"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>8</v>
       </c>
@@ -5809,12 +5806,12 @@
       <c r="N127" s="3">
         <v>2.73</v>
       </c>
-      <c r="O127" s="3">
+      <c r="O127" s="6">
         <f t="shared" si="3"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>8</v>
       </c>
@@ -5845,12 +5842,12 @@
       <c r="N128" s="3">
         <v>2.73</v>
       </c>
-      <c r="O128" s="3">
+      <c r="O128" s="6">
         <f t="shared" si="3"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>8</v>
       </c>
@@ -5883,12 +5880,12 @@
       <c r="N129" s="3">
         <v>2.73</v>
       </c>
-      <c r="O129" s="3">
+      <c r="O129" s="6">
         <f t="shared" si="3"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>8</v>
       </c>
@@ -5919,12 +5916,12 @@
       <c r="N130" s="3">
         <v>2.75</v>
       </c>
-      <c r="O130" s="3">
+      <c r="O130" s="6">
         <f t="shared" ref="O130:O142" si="4">N130-0.02</f>
         <v>2.73</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>8</v>
       </c>
@@ -5955,12 +5952,12 @@
       <c r="N131" s="3">
         <v>2.76</v>
       </c>
-      <c r="O131" s="3">
+      <c r="O131" s="6">
         <f t="shared" si="4"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>8</v>
       </c>
@@ -5993,12 +5990,12 @@
       <c r="N132" s="3">
         <v>2.76</v>
       </c>
-      <c r="O132" s="3">
+      <c r="O132" s="6">
         <f t="shared" si="4"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>8</v>
       </c>
@@ -6031,12 +6028,12 @@
       <c r="N133" s="3">
         <v>2.76</v>
       </c>
-      <c r="O133" s="3">
+      <c r="O133" s="6">
         <f t="shared" si="4"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>8</v>
       </c>
@@ -6069,12 +6066,12 @@
       <c r="N134" s="3">
         <v>2.8</v>
       </c>
-      <c r="O134" s="3">
+      <c r="O134" s="6">
         <f t="shared" si="4"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>8</v>
       </c>
@@ -6107,12 +6104,12 @@
       <c r="N135" s="3">
         <v>2.8</v>
       </c>
-      <c r="O135" s="3">
+      <c r="O135" s="6">
         <f t="shared" si="4"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>8</v>
       </c>
@@ -6145,12 +6142,12 @@
       <c r="N136" s="3">
         <v>2.8</v>
       </c>
-      <c r="O136" s="3">
+      <c r="O136" s="6">
         <f t="shared" si="4"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>8</v>
       </c>
@@ -6181,12 +6178,12 @@
       <c r="N137" s="3">
         <v>2.85</v>
       </c>
-      <c r="O137" s="3">
+      <c r="O137" s="6">
         <f t="shared" si="4"/>
         <v>2.83</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>8</v>
       </c>
@@ -6217,12 +6214,12 @@
       <c r="N138" s="3">
         <v>2.89</v>
       </c>
-      <c r="O138" s="3">
+      <c r="O138" s="6">
         <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>8</v>
       </c>
@@ -6253,12 +6250,12 @@
       <c r="N139" s="3">
         <v>2.95</v>
       </c>
-      <c r="O139" s="3">
+      <c r="O139" s="6">
         <f t="shared" si="4"/>
         <v>2.93</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>8</v>
       </c>
@@ -6289,12 +6286,12 @@
       <c r="N140" s="3">
         <v>2.95</v>
       </c>
-      <c r="O140" s="3">
+      <c r="O140" s="6">
         <f t="shared" si="4"/>
         <v>2.93</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>8</v>
       </c>
@@ -6325,12 +6322,12 @@
       <c r="N141" s="3">
         <v>3</v>
       </c>
-      <c r="O141" s="3">
+      <c r="O141" s="6">
         <f t="shared" si="4"/>
         <v>2.98</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>8</v>
       </c>
@@ -6361,13 +6358,13 @@
       <c r="N142" s="3">
         <v>3.15</v>
       </c>
-      <c r="O142" s="3">
+      <c r="O142" s="6">
         <f t="shared" si="4"/>
         <v>3.13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O185">
+  <sortState ref="A2:O185">
     <sortCondition ref="O1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/Пути на старую волочилку.xlsx
+++ b/excel/Пути на старую волочилку.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\Anjelika\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7346378A-0A83-40A7-ABBB-50E0F24E6776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16440"/>
+    <workbookView xWindow="38265" yWindow="2640" windowWidth="29070" windowHeight="15870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$P$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$O$138</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -369,24 +375,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O142"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O140"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="20.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -433,7 +439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>8</v>
       </c>
@@ -477,11 +483,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="O2" s="4">
-        <f t="shared" ref="O2:O33" si="0">N2-0.02</f>
+        <f t="shared" ref="O2:O65" si="0">N2-0.02</f>
         <v>1.1099999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>8</v>
       </c>
@@ -529,7 +535,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>8</v>
       </c>
@@ -577,7 +583,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>8</v>
       </c>
@@ -625,7 +631,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -673,7 +679,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>8</v>
       </c>
@@ -721,7 +727,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -769,7 +775,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -817,7 +823,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -865,7 +871,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -913,7 +919,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -961,7 +967,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>8</v>
       </c>
@@ -1007,7 +1013,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -1055,7 +1061,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>8</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -1151,7 +1157,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>8</v>
       </c>
@@ -1199,7 +1205,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>8</v>
       </c>
@@ -1245,7 +1251,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>8</v>
       </c>
@@ -1291,7 +1297,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>8</v>
       </c>
@@ -1337,7 +1343,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>8</v>
       </c>
@@ -1383,7 +1389,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>8</v>
       </c>
@@ -1429,7 +1435,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>8</v>
       </c>
@@ -1475,7 +1481,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>8</v>
       </c>
@@ -1523,7 +1529,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>8</v>
       </c>
@@ -1569,7 +1575,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>8</v>
       </c>
@@ -1615,7 +1621,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>8</v>
       </c>
@@ -1661,7 +1667,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>8</v>
       </c>
@@ -1707,7 +1713,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>8</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>1.3599999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>8</v>
       </c>
@@ -1799,7 +1805,7 @@
         <v>1.3699999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>8</v>
       </c>
@@ -1845,7 +1851,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>8</v>
       </c>
@@ -1891,7 +1897,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>8</v>
       </c>
@@ -1937,7 +1943,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>8</v>
       </c>
@@ -1979,11 +1985,11 @@
         <v>1.4</v>
       </c>
       <c r="O34" s="4">
-        <f t="shared" ref="O34:O65" si="1">N34-0.02</f>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>8</v>
       </c>
@@ -2025,11 +2031,11 @@
         <v>1.4</v>
       </c>
       <c r="O35" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>8</v>
       </c>
@@ -2069,11 +2075,11 @@
         <v>1.4</v>
       </c>
       <c r="O36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>8</v>
       </c>
@@ -2115,11 +2121,11 @@
         <v>1.4</v>
       </c>
       <c r="O37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>8</v>
       </c>
@@ -2159,11 +2165,11 @@
         <v>1.45</v>
       </c>
       <c r="O38" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.43</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>8</v>
       </c>
@@ -2205,11 +2211,11 @@
         <v>1.45</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.43</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>8</v>
       </c>
@@ -2251,11 +2257,11 @@
         <v>1.45</v>
       </c>
       <c r="O40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.43</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>8</v>
       </c>
@@ -2295,11 +2301,11 @@
         <v>1.5</v>
       </c>
       <c r="O41" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.48</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>8</v>
       </c>
@@ -2339,11 +2345,11 @@
         <v>1.5</v>
       </c>
       <c r="O42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.48</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>8</v>
       </c>
@@ -2383,11 +2389,11 @@
         <v>1.55</v>
       </c>
       <c r="O43" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.53</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>8</v>
       </c>
@@ -2427,11 +2433,11 @@
         <v>1.55</v>
       </c>
       <c r="O44" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.53</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>8</v>
       </c>
@@ -2471,11 +2477,11 @@
         <v>1.55</v>
       </c>
       <c r="O45" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.53</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>8</v>
       </c>
@@ -2515,11 +2521,11 @@
         <v>1.55</v>
       </c>
       <c r="O46" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.53</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>8</v>
       </c>
@@ -2559,11 +2565,11 @@
         <v>1.6</v>
       </c>
       <c r="O47" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>8</v>
       </c>
@@ -2603,11 +2609,11 @@
         <v>1.6</v>
       </c>
       <c r="O48" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>8</v>
       </c>
@@ -2647,11 +2653,11 @@
         <v>1.6</v>
       </c>
       <c r="O49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>8</v>
       </c>
@@ -2691,11 +2697,11 @@
         <v>1.6</v>
       </c>
       <c r="O50" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>8</v>
       </c>
@@ -2735,11 +2741,11 @@
         <v>1.65</v>
       </c>
       <c r="O51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.63</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>8</v>
       </c>
@@ -2778,12 +2784,12 @@
       <c r="N52" s="3">
         <v>1.7</v>
       </c>
-      <c r="O52" s="6">
-        <f t="shared" si="1"/>
+      <c r="O52" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>8</v>
       </c>
@@ -2820,12 +2826,12 @@
       <c r="N53" s="3">
         <v>1.7</v>
       </c>
-      <c r="O53" s="6">
-        <f t="shared" si="1"/>
+      <c r="O53" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>8</v>
       </c>
@@ -2862,12 +2868,12 @@
       <c r="N54" s="3">
         <v>1.7</v>
       </c>
-      <c r="O54" s="6">
-        <f t="shared" si="1"/>
+      <c r="O54" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>8</v>
       </c>
@@ -2906,12 +2912,12 @@
       <c r="N55" s="3">
         <v>1.7</v>
       </c>
-      <c r="O55" s="6">
-        <f t="shared" si="1"/>
+      <c r="O55" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>8</v>
       </c>
@@ -2948,12 +2954,12 @@
       <c r="N56" s="3">
         <v>1.7</v>
       </c>
-      <c r="O56" s="6">
-        <f t="shared" si="1"/>
+      <c r="O56" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>8</v>
       </c>
@@ -2992,12 +2998,12 @@
       <c r="N57" s="3">
         <v>1.7</v>
       </c>
-      <c r="O57" s="6">
-        <f t="shared" si="1"/>
+      <c r="O57" s="4">
+        <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>8</v>
       </c>
@@ -3036,12 +3042,12 @@
       <c r="N58" s="3">
         <v>1.73</v>
       </c>
-      <c r="O58" s="6">
-        <f t="shared" si="1"/>
+      <c r="O58" s="4">
+        <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>8</v>
       </c>
@@ -3078,12 +3084,12 @@
       <c r="N59" s="3">
         <v>1.73</v>
       </c>
-      <c r="O59" s="6">
-        <f t="shared" si="1"/>
+      <c r="O59" s="4">
+        <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>8</v>
       </c>
@@ -3120,12 +3126,12 @@
       <c r="N60" s="3">
         <v>1.73</v>
       </c>
-      <c r="O60" s="6">
-        <f t="shared" si="1"/>
+      <c r="O60" s="4">
+        <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>8</v>
       </c>
@@ -3162,12 +3168,12 @@
       <c r="N61" s="3">
         <v>1.73</v>
       </c>
-      <c r="O61" s="6">
-        <f t="shared" si="1"/>
+      <c r="O61" s="4">
+        <f t="shared" si="0"/>
         <v>1.71</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>8</v>
       </c>
@@ -3204,12 +3210,12 @@
       <c r="N62" s="3">
         <v>1.75</v>
       </c>
-      <c r="O62" s="6">
-        <f t="shared" si="1"/>
+      <c r="O62" s="4">
+        <f t="shared" si="0"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>8</v>
       </c>
@@ -3248,12 +3254,12 @@
       <c r="N63" s="3">
         <v>1.75</v>
       </c>
-      <c r="O63" s="6">
-        <f t="shared" si="1"/>
+      <c r="O63" s="4">
+        <f t="shared" si="0"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>8</v>
       </c>
@@ -3290,12 +3296,12 @@
       <c r="N64" s="3">
         <v>1.75</v>
       </c>
-      <c r="O64" s="6">
-        <f t="shared" si="1"/>
+      <c r="O64" s="4">
+        <f t="shared" si="0"/>
         <v>1.73</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>8</v>
       </c>
@@ -3332,12 +3338,12 @@
       <c r="N65" s="3">
         <v>1.8</v>
       </c>
-      <c r="O65" s="6">
-        <f t="shared" si="1"/>
+      <c r="O65" s="4">
+        <f t="shared" si="0"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>8</v>
       </c>
@@ -3374,12 +3380,12 @@
       <c r="N66" s="3">
         <v>1.8</v>
       </c>
-      <c r="O66" s="6">
-        <f t="shared" ref="O66:O97" si="2">N66-0.02</f>
+      <c r="O66" s="4">
+        <f t="shared" ref="O66:O129" si="1">N66-0.02</f>
         <v>1.78</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>8</v>
       </c>
@@ -3416,12 +3422,12 @@
       <c r="N67" s="3">
         <v>1.8</v>
       </c>
-      <c r="O67" s="6">
-        <f t="shared" si="2"/>
+      <c r="O67" s="4">
+        <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>8</v>
       </c>
@@ -3458,12 +3464,12 @@
       <c r="N68" s="3">
         <v>1.8</v>
       </c>
-      <c r="O68" s="6">
-        <f t="shared" si="2"/>
+      <c r="O68" s="4">
+        <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>8</v>
       </c>
@@ -3500,12 +3506,12 @@
       <c r="N69" s="3">
         <v>1.8</v>
       </c>
-      <c r="O69" s="6">
-        <f t="shared" si="2"/>
+      <c r="O69" s="4">
+        <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>8</v>
       </c>
@@ -3542,12 +3548,12 @@
       <c r="N70" s="3">
         <v>1.85</v>
       </c>
-      <c r="O70" s="6">
-        <f t="shared" si="2"/>
+      <c r="O70" s="4">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>8</v>
       </c>
@@ -3584,12 +3590,12 @@
       <c r="N71" s="3">
         <v>1.9</v>
       </c>
-      <c r="O71" s="6">
-        <f t="shared" si="2"/>
+      <c r="O71" s="4">
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>8</v>
       </c>
@@ -3626,12 +3632,12 @@
       <c r="N72" s="3">
         <v>1.92</v>
       </c>
-      <c r="O72" s="6">
-        <f t="shared" si="2"/>
+      <c r="O72" s="4">
+        <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>8</v>
       </c>
@@ -3668,12 +3674,12 @@
       <c r="N73" s="3">
         <v>1.92</v>
       </c>
-      <c r="O73" s="6">
-        <f t="shared" si="2"/>
+      <c r="O73" s="4">
+        <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>8</v>
       </c>
@@ -3710,12 +3716,12 @@
       <c r="N74" s="3">
         <v>1.95</v>
       </c>
-      <c r="O74" s="6">
-        <f t="shared" si="2"/>
+      <c r="O74" s="4">
+        <f t="shared" si="1"/>
         <v>1.93</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>8</v>
       </c>
@@ -3752,12 +3758,12 @@
       <c r="N75" s="3">
         <v>1.95</v>
       </c>
-      <c r="O75" s="6">
-        <f t="shared" si="2"/>
+      <c r="O75" s="4">
+        <f t="shared" si="1"/>
         <v>1.93</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>8</v>
       </c>
@@ -3794,12 +3800,12 @@
       <c r="N76" s="3">
         <v>2</v>
       </c>
-      <c r="O76" s="6">
-        <f t="shared" si="2"/>
+      <c r="O76" s="4">
+        <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>8</v>
       </c>
@@ -3836,12 +3842,12 @@
       <c r="N77" s="3">
         <v>2</v>
       </c>
-      <c r="O77" s="6">
-        <f t="shared" si="2"/>
+      <c r="O77" s="4">
+        <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>8</v>
       </c>
@@ -3878,12 +3884,12 @@
       <c r="N78" s="3">
         <v>2</v>
       </c>
-      <c r="O78" s="6">
-        <f t="shared" si="2"/>
+      <c r="O78" s="4">
+        <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>8</v>
       </c>
@@ -3920,12 +3926,12 @@
       <c r="N79" s="3">
         <v>2.0299999999999998</v>
       </c>
-      <c r="O79" s="6">
-        <f t="shared" si="2"/>
+      <c r="O79" s="4">
+        <f t="shared" si="1"/>
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>8</v>
       </c>
@@ -3962,12 +3968,12 @@
       <c r="N80" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O80" s="6">
-        <f t="shared" si="2"/>
+      <c r="O80" s="4">
+        <f t="shared" si="1"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>8</v>
       </c>
@@ -4004,12 +4010,12 @@
       <c r="N81" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O81" s="6">
-        <f t="shared" si="2"/>
+      <c r="O81" s="4">
+        <f t="shared" si="1"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>8</v>
       </c>
@@ -4046,12 +4052,12 @@
       <c r="N82" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O82" s="6">
-        <f t="shared" si="2"/>
+      <c r="O82" s="4">
+        <f t="shared" si="1"/>
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>8</v>
       </c>
@@ -4086,12 +4092,12 @@
       <c r="N83" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O83" s="6">
-        <f t="shared" si="2"/>
+      <c r="O83" s="4">
+        <f t="shared" si="1"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>8</v>
       </c>
@@ -4126,12 +4132,12 @@
       <c r="N84" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O84" s="6">
-        <f t="shared" si="2"/>
+      <c r="O84" s="4">
+        <f t="shared" si="1"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>8</v>
       </c>
@@ -4168,12 +4174,12 @@
       <c r="N85" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O85" s="6">
-        <f t="shared" si="2"/>
+      <c r="O85" s="4">
+        <f t="shared" si="1"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>8</v>
       </c>
@@ -4210,13 +4216,15 @@
       <c r="N86" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O86" s="6">
-        <f t="shared" si="2"/>
+      <c r="O86" s="4">
+        <f t="shared" si="1"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="5"/>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
+        <v>8</v>
+      </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
@@ -4248,12 +4256,12 @@
       <c r="N87" s="3">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O87" s="6">
-        <f t="shared" si="2"/>
+      <c r="O87" s="4">
+        <f t="shared" si="1"/>
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>8</v>
       </c>
@@ -4288,12 +4296,12 @@
       <c r="N88" s="3">
         <v>2.1</v>
       </c>
-      <c r="O88" s="6">
-        <f t="shared" si="2"/>
+      <c r="O88" s="4">
+        <f t="shared" si="1"/>
         <v>2.08</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>8</v>
       </c>
@@ -4328,12 +4336,12 @@
       <c r="N89" s="3">
         <v>2.15</v>
       </c>
-      <c r="O89" s="6">
-        <f t="shared" si="2"/>
+      <c r="O89" s="4">
+        <f t="shared" si="1"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>8</v>
       </c>
@@ -4368,12 +4376,12 @@
       <c r="N90" s="3">
         <v>2.15</v>
       </c>
-      <c r="O90" s="6">
-        <f t="shared" si="2"/>
+      <c r="O90" s="4">
+        <f t="shared" si="1"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>8</v>
       </c>
@@ -4408,12 +4416,12 @@
       <c r="N91" s="3">
         <v>2.15</v>
       </c>
-      <c r="O91" s="6">
-        <f t="shared" si="2"/>
+      <c r="O91" s="4">
+        <f t="shared" si="1"/>
         <v>2.13</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>8</v>
       </c>
@@ -4448,12 +4456,12 @@
       <c r="N92" s="3">
         <v>2.1800000000000002</v>
       </c>
-      <c r="O92" s="6">
-        <f t="shared" si="2"/>
+      <c r="O92" s="4">
+        <f t="shared" si="1"/>
         <v>2.16</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>8</v>
       </c>
@@ -4488,12 +4496,12 @@
       <c r="N93" s="3">
         <v>2.1800000000000002</v>
       </c>
-      <c r="O93" s="6">
-        <f t="shared" si="2"/>
+      <c r="O93" s="4">
+        <f t="shared" si="1"/>
         <v>2.16</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>8</v>
       </c>
@@ -4528,12 +4536,12 @@
       <c r="N94" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O94" s="6">
-        <f t="shared" si="2"/>
+      <c r="O94" s="4">
+        <f t="shared" si="1"/>
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>8</v>
       </c>
@@ -4568,12 +4576,12 @@
       <c r="N95" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O95" s="6">
-        <f t="shared" si="2"/>
+      <c r="O95" s="4">
+        <f t="shared" si="1"/>
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>8</v>
       </c>
@@ -4608,12 +4616,12 @@
       <c r="N96" s="3">
         <v>2.25</v>
       </c>
-      <c r="O96" s="6">
-        <f t="shared" si="2"/>
+      <c r="O96" s="4">
+        <f t="shared" si="1"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>8</v>
       </c>
@@ -4648,12 +4656,12 @@
       <c r="N97" s="3">
         <v>2.25</v>
       </c>
-      <c r="O97" s="6">
-        <f t="shared" si="2"/>
+      <c r="O97" s="4">
+        <f t="shared" si="1"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>8</v>
       </c>
@@ -4688,12 +4696,12 @@
       <c r="N98" s="3">
         <v>2.25</v>
       </c>
-      <c r="O98" s="6">
-        <f t="shared" ref="O98:O129" si="3">N98-0.02</f>
+      <c r="O98" s="4">
+        <f t="shared" si="1"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>8</v>
       </c>
@@ -4728,12 +4736,12 @@
       <c r="N99" s="3">
         <v>2.25</v>
       </c>
-      <c r="O99" s="6">
-        <f t="shared" si="3"/>
+      <c r="O99" s="4">
+        <f t="shared" si="1"/>
         <v>2.23</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>8</v>
       </c>
@@ -4768,12 +4776,12 @@
       <c r="N100" s="3">
         <v>2.27</v>
       </c>
-      <c r="O100" s="6">
-        <f t="shared" si="3"/>
+      <c r="O100" s="4">
+        <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>8</v>
       </c>
@@ -4808,12 +4816,12 @@
       <c r="N101" s="3">
         <v>2.2799999999999998</v>
       </c>
-      <c r="O101" s="6">
-        <f t="shared" si="3"/>
+      <c r="O101" s="4">
+        <f t="shared" si="1"/>
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>8</v>
       </c>
@@ -4848,12 +4856,12 @@
       <c r="N102" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O102" s="6">
-        <f t="shared" si="3"/>
+      <c r="O102" s="4">
+        <f t="shared" si="1"/>
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>8</v>
       </c>
@@ -4888,12 +4896,12 @@
       <c r="N103" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O103" s="6">
-        <f t="shared" si="3"/>
+      <c r="O103" s="4">
+        <f t="shared" si="1"/>
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>8</v>
       </c>
@@ -4928,12 +4936,12 @@
       <c r="N104" s="3">
         <v>2.35</v>
       </c>
-      <c r="O104" s="6">
-        <f t="shared" si="3"/>
+      <c r="O104" s="4">
+        <f t="shared" si="1"/>
         <v>2.33</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>8</v>
       </c>
@@ -4966,12 +4974,12 @@
       <c r="N105" s="3">
         <v>2.35</v>
       </c>
-      <c r="O105" s="6">
-        <f t="shared" si="3"/>
+      <c r="O105" s="4">
+        <f t="shared" si="1"/>
         <v>2.33</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>8</v>
       </c>
@@ -5004,12 +5012,12 @@
       <c r="N106" s="3">
         <v>2.4</v>
       </c>
-      <c r="O106" s="6">
-        <f t="shared" si="3"/>
+      <c r="O106" s="4">
+        <f t="shared" si="1"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>8</v>
       </c>
@@ -5042,12 +5050,12 @@
       <c r="N107" s="3">
         <v>2.4</v>
       </c>
-      <c r="O107" s="6">
-        <f t="shared" si="3"/>
+      <c r="O107" s="4">
+        <f t="shared" si="1"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>8</v>
       </c>
@@ -5080,12 +5088,12 @@
       <c r="N108" s="3">
         <v>2.4</v>
       </c>
-      <c r="O108" s="6">
-        <f t="shared" si="3"/>
+      <c r="O108" s="4">
+        <f t="shared" si="1"/>
         <v>2.38</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>8</v>
       </c>
@@ -5118,12 +5126,12 @@
       <c r="N109" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O109" s="6">
-        <f t="shared" si="3"/>
+      <c r="O109" s="4">
+        <f t="shared" si="1"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>8</v>
       </c>
@@ -5156,12 +5164,12 @@
       <c r="N110" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O110" s="6">
-        <f t="shared" si="3"/>
+      <c r="O110" s="4">
+        <f t="shared" si="1"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>8</v>
       </c>
@@ -5194,12 +5202,12 @@
       <c r="N111" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O111" s="6">
-        <f t="shared" si="3"/>
+      <c r="O111" s="4">
+        <f t="shared" si="1"/>
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>8</v>
       </c>
@@ -5232,12 +5240,12 @@
       <c r="N112" s="3">
         <v>2.5</v>
       </c>
-      <c r="O112" s="6">
-        <f t="shared" si="3"/>
+      <c r="O112" s="4">
+        <f t="shared" si="1"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>8</v>
       </c>
@@ -5270,12 +5278,12 @@
       <c r="N113" s="3">
         <v>2.5</v>
       </c>
-      <c r="O113" s="6">
-        <f t="shared" si="3"/>
+      <c r="O113" s="4">
+        <f t="shared" si="1"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>8</v>
       </c>
@@ -5312,12 +5320,12 @@
       <c r="N114" s="3">
         <v>2.5</v>
       </c>
-      <c r="O114" s="6">
-        <f t="shared" si="3"/>
+      <c r="O114" s="4">
+        <f t="shared" si="1"/>
         <v>2.48</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>8</v>
       </c>
@@ -5352,12 +5360,12 @@
       <c r="N115" s="3">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O115" s="6">
-        <f t="shared" si="3"/>
+      <c r="O115" s="4">
+        <f t="shared" si="1"/>
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>8</v>
       </c>
@@ -5392,12 +5400,12 @@
       <c r="N116" s="3">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O116" s="6">
-        <f t="shared" si="3"/>
+      <c r="O116" s="4">
+        <f t="shared" si="1"/>
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>8</v>
       </c>
@@ -5430,12 +5438,12 @@
       <c r="N117" s="3">
         <v>2.6</v>
       </c>
-      <c r="O117" s="6">
-        <f t="shared" si="3"/>
+      <c r="O117" s="4">
+        <f t="shared" si="1"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>8</v>
       </c>
@@ -5468,12 +5476,12 @@
       <c r="N118" s="3">
         <v>2.6</v>
       </c>
-      <c r="O118" s="6">
-        <f t="shared" si="3"/>
+      <c r="O118" s="4">
+        <f t="shared" si="1"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>8</v>
       </c>
@@ -5506,12 +5514,12 @@
       <c r="N119" s="3">
         <v>2.6</v>
       </c>
-      <c r="O119" s="6">
-        <f t="shared" si="3"/>
+      <c r="O119" s="4">
+        <f t="shared" si="1"/>
         <v>2.58</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>8</v>
       </c>
@@ -5544,12 +5552,12 @@
       <c r="N120" s="3">
         <v>2.63</v>
       </c>
-      <c r="O120" s="6">
-        <f t="shared" si="3"/>
+      <c r="O120" s="4">
+        <f t="shared" si="1"/>
         <v>2.61</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>8</v>
       </c>
@@ -5582,12 +5590,12 @@
       <c r="N121" s="3">
         <v>2.65</v>
       </c>
-      <c r="O121" s="6">
-        <f t="shared" si="3"/>
+      <c r="O121" s="4">
+        <f t="shared" si="1"/>
         <v>2.63</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>8</v>
       </c>
@@ -5620,12 +5628,12 @@
       <c r="N122" s="3">
         <v>2.7</v>
       </c>
-      <c r="O122" s="6">
-        <f t="shared" si="3"/>
+      <c r="O122" s="4">
+        <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>8</v>
       </c>
@@ -5656,12 +5664,12 @@
       <c r="N123" s="3">
         <v>2.7</v>
       </c>
-      <c r="O123" s="6">
-        <f t="shared" si="3"/>
+      <c r="O123" s="4">
+        <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>8</v>
       </c>
@@ -5694,12 +5702,12 @@
       <c r="N124" s="3">
         <v>2.7</v>
       </c>
-      <c r="O124" s="6">
-        <f t="shared" si="3"/>
+      <c r="O124" s="4">
+        <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>8</v>
       </c>
@@ -5730,12 +5738,12 @@
       <c r="N125" s="3">
         <v>2.7</v>
       </c>
-      <c r="O125" s="6">
-        <f t="shared" si="3"/>
+      <c r="O125" s="4">
+        <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>8</v>
       </c>
@@ -5768,12 +5776,12 @@
       <c r="N126" s="3">
         <v>2.7</v>
       </c>
-      <c r="O126" s="6">
-        <f t="shared" si="3"/>
+      <c r="O126" s="4">
+        <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>8</v>
       </c>
@@ -5806,12 +5814,12 @@
       <c r="N127" s="3">
         <v>2.73</v>
       </c>
-      <c r="O127" s="6">
-        <f t="shared" si="3"/>
+      <c r="O127" s="4">
+        <f t="shared" si="1"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>8</v>
       </c>
@@ -5842,12 +5850,12 @@
       <c r="N128" s="3">
         <v>2.73</v>
       </c>
-      <c r="O128" s="6">
-        <f t="shared" si="3"/>
+      <c r="O128" s="4">
+        <f t="shared" si="1"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>8</v>
       </c>
@@ -5880,12 +5888,12 @@
       <c r="N129" s="3">
         <v>2.73</v>
       </c>
-      <c r="O129" s="6">
-        <f t="shared" si="3"/>
+      <c r="O129" s="4">
+        <f t="shared" si="1"/>
         <v>2.71</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>8</v>
       </c>
@@ -5916,12 +5924,12 @@
       <c r="N130" s="3">
         <v>2.75</v>
       </c>
-      <c r="O130" s="6">
-        <f t="shared" ref="O130:O142" si="4">N130-0.02</f>
+      <c r="O130" s="4">
+        <f t="shared" ref="O130:O138" si="2">N130-0.02</f>
         <v>2.73</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>8</v>
       </c>
@@ -5952,12 +5960,12 @@
       <c r="N131" s="3">
         <v>2.76</v>
       </c>
-      <c r="O131" s="6">
-        <f t="shared" si="4"/>
+      <c r="O131" s="4">
+        <f t="shared" si="2"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>8</v>
       </c>
@@ -5990,12 +5998,12 @@
       <c r="N132" s="3">
         <v>2.76</v>
       </c>
-      <c r="O132" s="6">
-        <f t="shared" si="4"/>
+      <c r="O132" s="4">
+        <f t="shared" si="2"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>8</v>
       </c>
@@ -6028,12 +6036,12 @@
       <c r="N133" s="3">
         <v>2.76</v>
       </c>
-      <c r="O133" s="6">
-        <f t="shared" si="4"/>
+      <c r="O133" s="4">
+        <f t="shared" si="2"/>
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>8</v>
       </c>
@@ -6066,12 +6074,12 @@
       <c r="N134" s="3">
         <v>2.8</v>
       </c>
-      <c r="O134" s="6">
-        <f t="shared" si="4"/>
+      <c r="O134" s="4">
+        <f t="shared" si="2"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>8</v>
       </c>
@@ -6104,12 +6112,12 @@
       <c r="N135" s="3">
         <v>2.8</v>
       </c>
-      <c r="O135" s="6">
-        <f t="shared" si="4"/>
+      <c r="O135" s="4">
+        <f t="shared" si="2"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>8</v>
       </c>
@@ -6142,12 +6150,12 @@
       <c r="N136" s="3">
         <v>2.8</v>
       </c>
-      <c r="O136" s="6">
-        <f t="shared" si="4"/>
+      <c r="O136" s="4">
+        <f t="shared" si="2"/>
         <v>2.78</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>8</v>
       </c>
@@ -6178,12 +6186,12 @@
       <c r="N137" s="3">
         <v>2.85</v>
       </c>
-      <c r="O137" s="6">
-        <f t="shared" si="4"/>
+      <c r="O137" s="4">
+        <f t="shared" si="2"/>
         <v>2.83</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>8</v>
       </c>
@@ -6214,157 +6222,48 @@
       <c r="N138" s="3">
         <v>2.89</v>
       </c>
-      <c r="O138" s="6">
-        <f t="shared" si="4"/>
+      <c r="O138" s="4">
+        <f t="shared" si="2"/>
         <v>2.87</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A139" s="5">
-        <v>8</v>
-      </c>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" s="5"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="I139" s="3">
-        <v>5.86</v>
-      </c>
-      <c r="J139" s="3">
-        <v>5.15</v>
-      </c>
-      <c r="K139" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="L139" s="3">
-        <v>2</v>
-      </c>
-      <c r="M139" s="3">
-        <v>3.4</v>
-      </c>
-      <c r="N139" s="3">
-        <v>2.95</v>
-      </c>
-      <c r="O139" s="6">
-        <f t="shared" si="4"/>
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A140" s="5">
-        <v>8</v>
-      </c>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="6"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" s="5"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
-      <c r="H140" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="I140" s="3">
-        <v>5.86</v>
-      </c>
-      <c r="J140" s="3">
-        <v>5.15</v>
-      </c>
-      <c r="K140" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="L140" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="M140" s="3">
-        <v>3.4</v>
-      </c>
-      <c r="N140" s="3">
-        <v>2.95</v>
-      </c>
-      <c r="O140" s="6">
-        <f t="shared" si="4"/>
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A141" s="5">
-        <v>8</v>
-      </c>
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-      <c r="F141" s="3"/>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="I141" s="3">
-        <v>5.86</v>
-      </c>
-      <c r="J141" s="3">
-        <v>5.15</v>
-      </c>
-      <c r="K141" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="L141" s="3">
-        <v>3.9</v>
-      </c>
-      <c r="M141" s="3">
-        <v>3.4</v>
-      </c>
-      <c r="N141" s="3">
-        <v>3</v>
-      </c>
-      <c r="O141" s="6">
-        <f t="shared" si="4"/>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="5">
-        <v>8</v>
-      </c>
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="I142" s="3">
-        <v>5.86</v>
-      </c>
-      <c r="J142" s="3">
-        <v>5.15</v>
-      </c>
-      <c r="K142" s="3">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="L142" s="3">
-        <v>4.25</v>
-      </c>
-      <c r="M142" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="N142" s="3">
-        <v>3.15</v>
-      </c>
-      <c r="O142" s="6">
-        <f t="shared" si="4"/>
-        <v>3.13</v>
-      </c>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="6"/>
     </row>
   </sheetData>
-  <sortState ref="A2:O185">
+  <autoFilter ref="A1:O138" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O183">
     <sortCondition ref="O1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
